--- a/artfynd/A 10680-2024 artfynd.xlsx
+++ b/artfynd/A 10680-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83549737</v>
+        <v>66924383</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,24 +703,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västragården västra, Nrk</t>
+          <t>Västragården, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492008.1387731688</v>
+        <v>491993</v>
       </c>
       <c r="R2" t="n">
-        <v>6570363.641984326</v>
+        <v>6570387</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +738,14 @@
           <t>Hidinge</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0B1A78CA-83E1-4FAE-80DC-1B11CD46B2C6</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-04-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-04-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,23 +756,564 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Skogsbryn mot väg</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>88391083</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Garphyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>492022</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6570404</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Dubbelsidig, ca 90</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joseph Anderson, Aina Pihlgren, Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83549737</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västragården västra, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>492008</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6570364</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0B1A78CA-83E1-4FAE-80DC-1B11CD46B2C6</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2005-04-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2005-04-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Henrik Josefsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Henrik Josefsson, Toni Berglund</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>83550190</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västragården västra, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>492017</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6570410</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>33BBD246-870D-4193-9908-79FC3FB5C71F</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2005-04-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2005-04-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>66924384</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västragården, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>491993</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6570387</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-07-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-07-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Skogsbryn mot väg</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>66924387</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västragården, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>492052</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6570427</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-07-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-07-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blanskog, sluttning</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
